--- a/benchmark/data/bench.xlsx
+++ b/benchmark/data/bench.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\merag\Git\BioRedis_engine\benchmark\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A39D9DC8-6B0E-487F-9E73-44429192DC1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFC2FF25-6D5E-4B09-89D2-4B4566065DAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,9 +36,6 @@
     <t>Note</t>
   </si>
   <si>
-    <t>GeneScript</t>
-  </si>
-  <si>
     <t>https://www.genscript.com/tools/sirna-target-finder</t>
   </si>
   <si>
@@ -117,10 +114,13 @@
     <t>https://en.vectorbuilder.com/tool/shrna-target-design.html</t>
   </si>
   <si>
-    <t>BioRedis-engine</t>
-  </si>
-  <si>
-    <t>https://github.com/jkubis96/BioRedis_engine</t>
+    <t>BIOREDIS-engine</t>
+  </si>
+  <si>
+    <t>GenScript</t>
+  </si>
+  <si>
+    <t>https://github.com/jkubis96/BIOREDIS_engine</t>
   </si>
 </sst>
 </file>
@@ -479,64 +479,64 @@
         <v>2</v>
       </c>
       <c r="F1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1" t="s">
         <v>24</v>
-      </c>
-      <c r="H1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
         <v>22</v>
-      </c>
-      <c r="H3" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
         <v>17</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -544,57 +544,57 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="s">
         <v>27</v>
-      </c>
-      <c r="C12" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">

--- a/benchmark/data/bench.xlsx
+++ b/benchmark/data/bench.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\merag\Git\BioRedis_engine\benchmark\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFC2FF25-6D5E-4B09-89D2-4B4566065DAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A5CDFE8-46D5-4FBE-ABD4-89C90EBB3EA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,9 +42,6 @@
     <t>https://eurofinsgenomics.eu/en/ecom/tools/sirna-design/</t>
   </si>
   <si>
-    <t>Eurofinsgenomics</t>
-  </si>
-  <si>
     <t>https://horizondiscovery.com/en/ordering-and-calculation-tools/sidesign-center</t>
   </si>
   <si>
@@ -114,13 +111,16 @@
     <t>https://en.vectorbuilder.com/tool/shrna-target-design.html</t>
   </si>
   <si>
-    <t>BIOREDIS-engine</t>
-  </si>
-  <si>
     <t>GenScript</t>
   </si>
   <si>
     <t>https://github.com/jkubis96/BIOREDIS_engine</t>
+  </si>
+  <si>
+    <t>Eurofins Genomics</t>
+  </si>
+  <si>
+    <t>BIOREDIS</t>
   </si>
 </sst>
 </file>
@@ -479,64 +479,64 @@
         <v>2</v>
       </c>
       <c r="F1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" t="s">
         <v>23</v>
-      </c>
-      <c r="H1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
         <v>21</v>
-      </c>
-      <c r="H3" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
         <v>16</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -544,57 +544,57 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
         <v>26</v>
-      </c>
-      <c r="C12" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
